--- a/Assets/Data/DataTable/01_Character_Table.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kwon-yeodi/Documents/GitHub/Astrocat-2DSFProject/Assets/Data/DataTable/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Astrocats\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBBEE01-D457-E741-A07D-5034200B6849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D424D4BA-0070-43B7-8B8E-76AE88F3F8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="880" windowWidth="26360" windowHeight="20180" firstSheet="1" activeTab="1" xr2:uid="{9C87D5F5-8BEA-4097-972C-AE5594D6987B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9C87D5F5-8BEA-4097-972C-AE5594D6987B}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="3" r:id="rId1"/>
@@ -36,8 +36,28 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={ADC7BD43-605B-4A15-B63F-C1772D243909}</author>
+  </authors>
+  <commentList>
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{ADC7BD43-605B-4A15-B63F-C1772D243909}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    0: None
+1: Player
+2: Enemy</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="100">
   <si>
     <t>칼럼명</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -300,17 +320,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>enum:ELEMENT_TYPE:NONE</t>
-  </si>
-  <si>
     <t>Char_Default_Speed</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Skill3_ID</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Char_Name_001</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -323,14 +336,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Char_Name_004</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Char_Name_005</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>player_Rifleman</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -343,14 +348,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>player_Firebat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>player_Antitank</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>에셋 파일</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -364,6 +361,84 @@
   </si>
   <si>
     <t>Char_Default_Defense</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 아군 구분</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:SIDE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Side</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬_ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Char_Default_SP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 SP 보유량</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 SP 보유량</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Char_Max_SP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Char_Max_HP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mob_Name_1001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>penguin_Rfleman</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mob_Name_1002</t>
+  </si>
+  <si>
+    <t>penguin_Sniper</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mob_Name_1003</t>
+  </si>
+  <si>
+    <t>penguin_Commander</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mob_Name_1004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>penguin_Berserker</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -371,7 +446,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,6 +503,12 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -498,7 +579,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -584,13 +665,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -693,6 +833,54 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -791,8 +979,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15607925" y="4282247"/>
-          <a:ext cx="3978731" cy="6916482"/>
+          <a:off x="15592984" y="4170189"/>
+          <a:ext cx="3974996" cy="7028540"/>
           <a:chOff x="1529709" y="-180912"/>
           <a:chExt cx="3987802" cy="6854849"/>
         </a:xfrm>
@@ -3871,6 +4059,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="동우 제" id="{2012398A-2417-46A6-866B-A42EF62887C4}" userId="b4acf424e0b596a4" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4188,21 +4382,31 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C4" dT="2025-10-21T06:43:27.45" personId="{2012398A-2417-46A6-866B-A42EF62887C4}" id="{ADC7BD43-605B-4A15-B63F-C1772D243909}">
+    <text>0: None
+1: Player
+2: Enemy</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C094FC-05DB-4CD8-97F7-07905908E4F3}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" customWidth="1"/>
-    <col min="4" max="4" width="27.83203125" customWidth="1"/>
-    <col min="5" max="5" width="94.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.625" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="4" max="4" width="27.875" customWidth="1"/>
+    <col min="5" max="5" width="94.625" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="11" max="11" width="111.1640625" customWidth="1"/>
+    <col min="11" max="11" width="111.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29.25" customHeight="1">
+    <row r="1" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -4225,7 +4429,7 @@
       <c r="J1" s="32"/>
       <c r="K1" s="33"/>
     </row>
-    <row r="2" spans="1:11" ht="28.5" customHeight="1">
+    <row r="2" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
@@ -4252,7 +4456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="36">
+    <row r="3" spans="1:11" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>14</v>
       </c>
@@ -4279,7 +4483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="72">
+    <row r="4" spans="1:11" ht="66" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>21</v>
       </c>
@@ -4306,7 +4510,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="35.25" customHeight="1">
+    <row r="5" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>28</v>
       </c>
@@ -4333,7 +4537,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="39" customHeight="1">
+    <row r="6" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>34</v>
       </c>
@@ -4360,7 +4564,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="57" customHeight="1">
+    <row r="7" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>41</v>
       </c>
@@ -4387,7 +4591,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="51" customHeight="1">
+    <row r="8" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>47</v>
       </c>
@@ -4404,7 +4608,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="49.5" customHeight="1">
+    <row r="9" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>51</v>
       </c>
@@ -4421,7 +4625,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="57.75" customHeight="1">
+    <row r="10" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>54</v>
       </c>
@@ -4438,7 +4642,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="40.5" customHeight="1">
+    <row r="11" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>57</v>
       </c>
@@ -4453,7 +4657,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="40.5" customHeight="1">
+    <row r="12" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>61</v>
       </c>
@@ -4479,24 +4683,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B84F12-225E-4602-82FB-B79E6E932B4F}">
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B84F12-225E-4602-82FB-B79E6E932B4F}">
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="20.33203125" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="31" customWidth="1"/>
-    <col min="11" max="11" width="32" customWidth="1"/>
-    <col min="12" max="12" width="27" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" customWidth="1"/>
+    <col min="1" max="9" width="20.375" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="35" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="31" customWidth="1"/>
+    <col min="13" max="13" width="32" customWidth="1"/>
+    <col min="14" max="14" width="27" customWidth="1"/>
+    <col min="15" max="15" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="24.75" customHeight="1">
+    <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="18">
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>7</v>
       </c>
@@ -4504,40 +4709,37 @@
         <v>65</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="D2" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>35</v>
-      </c>
       <c r="G2" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>55</v>
+      <c r="J2" s="36" t="s">
+        <v>83</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="M2" s="17" t="s">
-        <v>82</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="L2" s="16"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>66</v>
       </c>
@@ -4545,40 +4747,37 @@
         <v>66</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>67</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>67</v>
       </c>
       <c r="H3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="K3" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>66</v>
-      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:13" ht="18">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -4586,266 +4785,286 @@
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>70</v>
+      <c r="G4" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" s="31" t="s">
-        <v>83</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="5"/>
+      <c r="N4" s="5"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>10010001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
         <v>100</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="34">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2">
         <v>40</v>
-      </c>
-      <c r="E5" s="2">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2">
-        <v>3</v>
       </c>
       <c r="G5" s="2">
         <v>10</v>
       </c>
-      <c r="H5" s="3">
-        <v>20010001</v>
-      </c>
-      <c r="I5" s="3">
-        <v>20010002</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="10">
+      <c r="H5" s="2">
         <v>3</v>
       </c>
-      <c r="L5" s="29">
-        <v>2</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>77</v>
-      </c>
+      <c r="I5" s="2">
+        <v>10</v>
+      </c>
+      <c r="J5" s="39"/>
+      <c r="K5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="29"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>10010002</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
         <v>100</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="48">
+        <v>9</v>
+      </c>
+      <c r="F6" s="2">
         <v>40</v>
-      </c>
-      <c r="E6" s="2">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2">
-        <v>3</v>
       </c>
       <c r="G6" s="2">
         <v>10</v>
       </c>
-      <c r="H6" s="3">
-        <v>20020001</v>
-      </c>
-      <c r="I6" s="3">
-        <v>20020002</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="10">
+      <c r="H6" s="2">
         <v>3</v>
       </c>
-      <c r="L6" s="29">
-        <v>2</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>78</v>
-      </c>
+      <c r="I6" s="2">
+        <v>10</v>
+      </c>
+      <c r="J6" s="39"/>
+      <c r="K6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="29"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>10010003</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="30">
         <v>100</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="49">
+        <v>9</v>
+      </c>
+      <c r="F7" s="46">
         <v>40</v>
-      </c>
-      <c r="E7" s="2">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2">
-        <v>3</v>
       </c>
       <c r="G7" s="2">
         <v>10</v>
       </c>
-      <c r="H7" s="3">
-        <v>20030001</v>
-      </c>
-      <c r="I7" s="3">
-        <v>20030002</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="10">
+      <c r="H7" s="2">
         <v>3</v>
       </c>
-      <c r="L7" s="29">
+      <c r="I7" s="2">
+        <v>10</v>
+      </c>
+      <c r="J7" s="39"/>
+      <c r="K7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="29"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="40">
+        <v>3001001</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="2">
         <v>2</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="D8" s="45">
+        <v>100</v>
+      </c>
+      <c r="E8" s="49">
+        <v>9</v>
+      </c>
+      <c r="F8" s="47">
+        <v>40</v>
+      </c>
+      <c r="G8" s="41">
+        <v>10</v>
+      </c>
+      <c r="H8" s="41">
+        <v>3</v>
+      </c>
+      <c r="I8" s="41">
+        <v>10</v>
+      </c>
+      <c r="J8" s="42"/>
+      <c r="K8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L8" s="43"/>
+      <c r="M8" s="10"/>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="6">
-        <v>10010004</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="40">
+        <v>3001002</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="30">
         <v>100</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E9" s="49">
+        <v>9</v>
+      </c>
+      <c r="F9" s="46">
         <v>40</v>
-      </c>
-      <c r="E8" s="2">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2">
-        <v>10</v>
-      </c>
-      <c r="H8" s="3">
-        <v>20040001</v>
-      </c>
-      <c r="I8" s="3">
-        <v>20040002</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="10">
-        <v>3</v>
-      </c>
-      <c r="L8" s="29">
-        <v>2</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6">
-        <v>10010005</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="2">
-        <v>100</v>
-      </c>
-      <c r="D9" s="2">
-        <v>40</v>
-      </c>
-      <c r="E9" s="2">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2">
-        <v>3</v>
       </c>
       <c r="G9" s="2">
         <v>10</v>
       </c>
-      <c r="H9" s="3">
-        <v>20050001</v>
-      </c>
-      <c r="I9" s="3">
-        <v>20050002</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="10">
+      <c r="H9" s="2">
         <v>3</v>
       </c>
-      <c r="L9" s="29">
+      <c r="I9" s="2">
+        <v>10</v>
+      </c>
+      <c r="J9" s="44"/>
+      <c r="K9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L9" s="43"/>
+      <c r="M9" s="10"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="40">
+        <v>3001003</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="2">
         <v>2</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>81</v>
-      </c>
+      <c r="D10" s="30">
+        <v>100</v>
+      </c>
+      <c r="E10" s="49">
+        <v>9</v>
+      </c>
+      <c r="F10" s="46">
+        <v>40</v>
+      </c>
+      <c r="G10" s="2">
+        <v>10</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2">
+        <v>10</v>
+      </c>
+      <c r="J10" s="44"/>
+      <c r="K10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10" s="43"/>
+      <c r="M10" s="10"/>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="2"/>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="40">
+        <v>3001004</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="30">
+        <v>100</v>
+      </c>
+      <c r="E11" s="49">
+        <v>9</v>
+      </c>
+      <c r="F11" s="46">
+        <v>40</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10</v>
+      </c>
+      <c r="H11" s="2">
+        <v>3</v>
+      </c>
+      <c r="I11" s="2">
+        <v>10</v>
+      </c>
+      <c r="J11" s="44"/>
+      <c r="K11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" s="43"/>
+      <c r="M11" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Data/DataTable/01_Character_Table.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Astrocats\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D424D4BA-0070-43B7-8B8E-76AE88F3F8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC29BAAB-52A4-4BBA-97B3-4DF76A88DF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9C87D5F5-8BEA-4097-972C-AE5594D6987B}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="127">
   <si>
     <t>칼럼명</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -368,14 +368,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>enum:SIDE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Side</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬_ID</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -439,6 +431,122 @@
   </si>
   <si>
     <t>penguin_Berserker</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:CHARACTER_SIDE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Char_Side</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염 속성 게이지 효율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 속성 게이지 효율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방사능 속성 게이지 효율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중력 속성 게이지 효율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공허 속성 게이지 효율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신성 속성 게이지 효율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Charge_Rate_Physics</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Charge_Rate_Flame</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Charge_Rate_Radioactive</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Charge_Rate_Gravity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Charge_Rate_Void</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Charge_Rate_Holy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Charge_Resiste</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 속성 과부하 계수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overload_Rate_Physics</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overload_Rate_Flame</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염 속성 과부하 계수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방사능 속성 과부하 계수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중력 속성 과부하 계수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공허 속성 과부하 계수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신성 속성 과부하 계수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overload_Rate_Radioactive</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overload_Rate_Gravity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overload_Rate_Void</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overload_Rate_Holy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20010001,20010002,20010003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>속성 게이지 저항 계수</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -446,7 +554,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,12 +611,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -730,7 +832,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -739,9 +841,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -755,14 +854,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -815,25 +908,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -860,9 +941,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -875,10 +953,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4394,6 +4481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C094FC-05DB-4CD8-97F7-07905908E4F3}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4407,249 +4495,249 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="44"/>
     </row>
     <row r="2" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="22">
         <v>1</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="17" t="s">
         <v>18</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="66" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="22">
         <v>2</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="18" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="22">
         <v>3</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="19" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="22">
         <v>4</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="20" t="s">
         <v>38</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="11" t="s">
         <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="22">
         <v>5</v>
       </c>
-      <c r="I7" s="24" t="s">
+      <c r="I7" s="21" t="s">
         <v>44</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="7" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="11" t="s">
         <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D11" s="2"/>
@@ -4658,13 +4746,13 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="11" t="s">
         <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="10" t="s">
         <v>59</v>
       </c>
       <c r="D12" s="2"/>
@@ -4684,138 +4772,267 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B84F12-225E-4602-82FB-B79E6E932B4F}">
-  <dimension ref="A1:N11"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="9" width="20.375" customWidth="1"/>
-    <col min="10" max="10" width="20.375" style="35" customWidth="1"/>
-    <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="12" max="12" width="31" customWidth="1"/>
-    <col min="13" max="13" width="32" customWidth="1"/>
-    <col min="14" max="14" width="27" customWidth="1"/>
-    <col min="15" max="15" width="20.625" customWidth="1"/>
+    <col min="1" max="2" width="20.375" customWidth="1"/>
+    <col min="3" max="3" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="20.375" customWidth="1"/>
+    <col min="10" max="10" width="28" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.125" style="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.125" style="28" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23" style="28" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.625" style="28" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.375" style="28" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.75" style="28" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="20.375" style="28" customWidth="1"/>
+    <col min="23" max="23" width="21" customWidth="1"/>
+    <col min="24" max="24" width="31" customWidth="1"/>
+    <col min="25" max="25" width="32" customWidth="1"/>
+    <col min="26" max="26" width="27" customWidth="1"/>
+    <col min="27" max="27" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="U2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="W2" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="X2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="L2" s="16"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
+      <c r="F4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N4" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="P4" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q4" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="R4" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="S4" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="T4" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="U4" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="V4" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="W4" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="X4" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y4" s="26"/>
+      <c r="Z4" s="26"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="8"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J4" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="L4" s="5"/>
-      <c r="N4" s="5"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>10010001</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -4827,7 +5044,7 @@
       <c r="D5" s="2">
         <v>100</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="27">
         <v>9</v>
       </c>
       <c r="F5" s="2">
@@ -4842,16 +5059,30 @@
       <c r="I5" s="2">
         <v>10</v>
       </c>
-      <c r="J5" s="39"/>
-      <c r="K5" s="2" t="s">
+      <c r="J5" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="29"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>10010002</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -4863,7 +5094,7 @@
       <c r="D6" s="2">
         <v>100</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="40">
         <v>9</v>
       </c>
       <c r="F6" s="2">
@@ -4878,16 +5109,28 @@
       <c r="I6" s="2">
         <v>10</v>
       </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="2" t="s">
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="29"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>10010003</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -4896,13 +5139,13 @@
       <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>100</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="41">
         <v>9</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="38">
         <v>40</v>
       </c>
       <c r="G7" s="2">
@@ -4914,66 +5157,91 @@
       <c r="I7" s="2">
         <v>10</v>
       </c>
-      <c r="J7" s="39"/>
-      <c r="K7" s="2" t="s">
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="32"/>
+      <c r="T7" s="32"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="32"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="29"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="40">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A8" s="33">
         <v>3001001</v>
       </c>
-      <c r="B8" s="41" t="s">
-        <v>92</v>
+      <c r="B8" s="34" t="s">
+        <v>90</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
-      <c r="D8" s="45">
+      <c r="D8" s="37">
         <v>100</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="41">
         <v>9</v>
       </c>
-      <c r="F8" s="47">
+      <c r="F8" s="39">
         <v>40</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="34">
         <v>10</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="34">
         <v>3</v>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="34">
         <v>10</v>
       </c>
-      <c r="J8" s="42"/>
-      <c r="K8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="L8" s="43"/>
-      <c r="M8" s="10"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="42"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="42"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="42"/>
+      <c r="V8" s="42"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="40">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A9" s="33">
         <v>3001002</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2">
         <v>2</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>100</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="41">
         <v>9</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="38">
         <v>40</v>
       </c>
       <c r="G9" s="2">
@@ -4985,30 +5253,43 @@
       <c r="I9" s="2">
         <v>10</v>
       </c>
-      <c r="J9" s="44"/>
-      <c r="K9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L9" s="43"/>
-      <c r="M9" s="10"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="42"/>
+      <c r="V9" s="42"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="40">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A10" s="33">
         <v>3001003</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="25">
         <v>100</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="41">
         <v>9</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="38">
         <v>40</v>
       </c>
       <c r="G10" s="2">
@@ -5020,30 +5301,43 @@
       <c r="I10" s="2">
         <v>10</v>
       </c>
-      <c r="J10" s="44"/>
-      <c r="K10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L10" s="43"/>
-      <c r="M10" s="10"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="42"/>
+      <c r="T10" s="42"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="42"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="40">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A11" s="33">
         <v>3001004</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="25">
         <v>100</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="41">
         <v>9</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="38">
         <v>40</v>
       </c>
       <c r="G11" s="2">
@@ -5055,12 +5349,25 @@
       <c r="I11" s="2">
         <v>10</v>
       </c>
-      <c r="J11" s="44"/>
-      <c r="K11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="L11" s="43"/>
-      <c r="M11" s="10"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="42"/>
+      <c r="V11" s="42"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Assets/Data/DataTable/01_Character_Table.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC29BAAB-52A4-4BBA-97B3-4DF76A88DF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB88A94-BF85-4295-B528-D7EC1ECB053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9C87D5F5-8BEA-4097-972C-AE5594D6987B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9C87D5F5-8BEA-4097-972C-AE5594D6987B}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="3" r:id="rId1"/>
@@ -39,10 +39,24 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={AF605D7A-2772-4B6B-9D24-C9A48EDF7BB3}</author>
     <author>tc={ADC7BD43-605B-4A15-B63F-C1772D243909}</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{ADC7BD43-605B-4A15-B63F-C1772D243909}">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{AF605D7A-2772-4B6B-9D24-C9A48EDF7BB3}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    1: 물리
+2: 화염
+3: 방사능
+4: 중력
+5: 공허
+6: 신성</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="1" shapeId="0" xr:uid="{ADC7BD43-605B-4A15-B63F-C1772D243909}">
       <text>
         <t>[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -57,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="110">
   <si>
     <t>칼럼명</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -442,111 +456,43 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>화염 속성 게이지 효율</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 속성 게이지 효율</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>방사능 속성 게이지 효율</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중력 속성 게이지 효율</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공허 속성 게이지 효율</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>신성 속성 게이지 효율</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Element_Charge_Rate_Physics</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Element_Charge_Rate_Flame</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Element_Charge_Rate_Radioactive</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Element_Charge_Rate_Gravity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Element_Charge_Rate_Void</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Element_Charge_Rate_Holy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Element_Charge_Resiste</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>물리 속성 과부하 계수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overload_Rate_Physics</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overload_Rate_Flame</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염 속성 과부하 계수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>방사능 속성 과부하 계수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중력 속성 과부하 계수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공허 속성 과부하 계수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>신성 속성 과부하 계수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overload_Rate_Radioactive</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overload_Rate_Gravity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overload_Rate_Void</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Overload_Rate_Holy</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>20010001,20010002,20010003</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>속성 게이지 저항 계수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>속성 게이지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Charge_Rate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>double[]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0,1.0,1.0,1.0,1.0,1.0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>속성 과부하 계수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Overload_Rate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -554,7 +500,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,6 +557,12 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -681,7 +633,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -741,118 +693,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1" tint="0.499984740745262"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1" tint="0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color theme="1" tint="0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -868,15 +720,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -908,65 +751,53 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4471,6 +4302,14 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="K3" dT="2025-10-22T06:27:13.54" personId="{2012398A-2417-46A6-866B-A42EF62887C4}" id="{AF605D7A-2772-4B6B-9D24-C9A48EDF7BB3}">
+    <text>1: 물리
+2: 화염
+3: 방사능
+4: 중력
+5: 공허
+6: 신성</text>
+  </threadedComment>
   <threadedComment ref="C4" dT="2025-10-21T06:43:27.45" personId="{2012398A-2417-46A6-866B-A42EF62887C4}" id="{ADC7BD43-605B-4A15-B63F-C1772D243909}">
     <text>0: None
 1: Player
@@ -4495,268 +4334,268 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="44"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="14">
         <v>1</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="66" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="1"/>
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="14">
         <v>2</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="14">
         <v>3</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="14">
         <v>4</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="7" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="14">
         <v>5</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4773,601 +4612,569 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B84F12-225E-4602-82FB-B79E6E932B4F}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="23.25" bestFit="1" customWidth="1"/>
     <col min="4" max="9" width="20.375" customWidth="1"/>
-    <col min="10" max="10" width="28" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="32.5" style="28" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.125" style="28" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.125" style="28" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26" style="28" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23" style="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.625" style="28" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.375" style="28" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.75" style="28" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="20.375" style="28" customWidth="1"/>
-    <col min="23" max="23" width="21" customWidth="1"/>
-    <col min="24" max="24" width="31" customWidth="1"/>
-    <col min="25" max="25" width="32" customWidth="1"/>
-    <col min="26" max="26" width="27" customWidth="1"/>
-    <col min="27" max="27" width="20.625" customWidth="1"/>
+    <col min="10" max="10" width="28" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.125" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.125" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26" style="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="36.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23" style="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23" style="17" customWidth="1"/>
+    <col min="20" max="20" width="21.625" style="17" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.375" style="17" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.75" style="17" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="20.375" style="17" customWidth="1"/>
+    <col min="25" max="25" width="21" customWidth="1"/>
+    <col min="26" max="26" width="31" customWidth="1"/>
+    <col min="27" max="27" width="32" customWidth="1"/>
+    <col min="28" max="28" width="27" customWidth="1"/>
+    <col min="29" max="29" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="N2" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="24"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="M4" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="30">
+        <v>10010001</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="14">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14">
+        <v>100</v>
+      </c>
+      <c r="E5" s="18">
+        <v>9</v>
+      </c>
+      <c r="F5" s="14">
+        <v>40</v>
+      </c>
+      <c r="G5" s="14">
+        <v>10</v>
+      </c>
+      <c r="H5" s="14">
+        <v>3</v>
+      </c>
+      <c r="I5" s="14">
+        <v>10</v>
+      </c>
+      <c r="J5" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="K5" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="L5" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="M5" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="31"/>
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="31"/>
+      <c r="AB5" s="31"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="30">
+        <v>10010002</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="14">
+        <v>1</v>
+      </c>
+      <c r="D6" s="14">
         <v>100</v>
       </c>
-      <c r="M2" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="T2" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="U2" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="V2" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="W2" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="X2" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
+      <c r="E6" s="18">
+        <v>9</v>
+      </c>
+      <c r="F6" s="14">
+        <v>40</v>
+      </c>
+      <c r="G6" s="14">
+        <v>10</v>
+      </c>
+      <c r="H6" s="14">
+        <v>3</v>
+      </c>
+      <c r="I6" s="14">
+        <v>10</v>
+      </c>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="31"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="31"/>
+      <c r="AB6" s="31"/>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J3" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="30">
+        <v>10010003</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="14">
+        <v>1</v>
+      </c>
+      <c r="D7" s="14">
+        <v>100</v>
+      </c>
+      <c r="E7" s="18">
+        <v>9</v>
+      </c>
+      <c r="F7" s="14">
+        <v>40</v>
+      </c>
+      <c r="G7" s="14">
+        <v>10</v>
+      </c>
+      <c r="H7" s="14">
+        <v>3</v>
+      </c>
+      <c r="I7" s="14">
+        <v>10</v>
+      </c>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="31"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="N4" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="O4" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="P4" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q4" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="R4" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="S4" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="T4" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="U4" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="V4" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="W4" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="X4" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="26"/>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" s="30">
+        <v>3001001</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="14">
+        <v>2</v>
+      </c>
+      <c r="D8" s="14">
+        <v>100</v>
+      </c>
+      <c r="E8" s="18">
+        <v>9</v>
+      </c>
+      <c r="F8" s="14">
+        <v>40</v>
+      </c>
+      <c r="G8" s="14">
+        <v>10</v>
+      </c>
+      <c r="H8" s="14">
+        <v>3</v>
+      </c>
+      <c r="I8" s="14">
+        <v>10</v>
+      </c>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="32"/>
+      <c r="Y8" s="32"/>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="32"/>
+      <c r="AB8" s="32"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>10010001</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" s="30">
+        <v>3001002</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="14">
+        <v>2</v>
+      </c>
+      <c r="D9" s="14">
         <v>100</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E9" s="18">
         <v>9</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F9" s="14">
         <v>40</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G9" s="14">
         <v>10</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H9" s="14">
         <v>3</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I9" s="14">
         <v>10</v>
       </c>
-      <c r="J5" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="32"/>
-      <c r="U5" s="32"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="32"/>
+      <c r="T9" s="32"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="32"/>
+      <c r="W9" s="32"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="32"/>
+      <c r="Z9" s="32"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="32"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>10010002</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A10" s="30">
+        <v>3001003</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="14">
+        <v>2</v>
+      </c>
+      <c r="D10" s="14">
         <v>100</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E10" s="18">
         <v>9</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F10" s="14">
         <v>40</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G10" s="14">
         <v>10</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H10" s="14">
         <v>3</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I10" s="14">
         <v>10</v>
       </c>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32"/>
-      <c r="S6" s="32"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="32"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="32"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>10010003</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" s="30">
+        <v>3001004</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="14">
+        <v>2</v>
+      </c>
+      <c r="D11" s="14">
         <v>100</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E11" s="18">
         <v>9</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F11" s="14">
         <v>40</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G11" s="14">
         <v>10</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H11" s="14">
         <v>3</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I11" s="14">
         <v>10</v>
       </c>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
-      <c r="R7" s="32"/>
-      <c r="S7" s="32"/>
-      <c r="T7" s="32"/>
-      <c r="U7" s="32"/>
-      <c r="V7" s="32"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="33">
-        <v>3001001</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="37">
-        <v>100</v>
-      </c>
-      <c r="E8" s="41">
-        <v>9</v>
-      </c>
-      <c r="F8" s="39">
-        <v>40</v>
-      </c>
-      <c r="G8" s="34">
-        <v>10</v>
-      </c>
-      <c r="H8" s="34">
-        <v>3</v>
-      </c>
-      <c r="I8" s="34">
-        <v>10</v>
-      </c>
-      <c r="J8" s="35"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42"/>
-      <c r="T8" s="42"/>
-      <c r="U8" s="42"/>
-      <c r="V8" s="42"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="33">
-        <v>3001002</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="25">
-        <v>100</v>
-      </c>
-      <c r="E9" s="41">
-        <v>9</v>
-      </c>
-      <c r="F9" s="38">
-        <v>40</v>
-      </c>
-      <c r="G9" s="2">
-        <v>10</v>
-      </c>
-      <c r="H9" s="2">
-        <v>3</v>
-      </c>
-      <c r="I9" s="2">
-        <v>10</v>
-      </c>
-      <c r="J9" s="36"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
-      <c r="T9" s="42"/>
-      <c r="U9" s="42"/>
-      <c r="V9" s="42"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="33">
-        <v>3001003</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="25">
-        <v>100</v>
-      </c>
-      <c r="E10" s="41">
-        <v>9</v>
-      </c>
-      <c r="F10" s="38">
-        <v>40</v>
-      </c>
-      <c r="G10" s="2">
-        <v>10</v>
-      </c>
-      <c r="H10" s="2">
-        <v>3</v>
-      </c>
-      <c r="I10" s="2">
-        <v>10</v>
-      </c>
-      <c r="J10" s="36"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="42"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="42"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="33">
-        <v>3001004</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="25">
-        <v>100</v>
-      </c>
-      <c r="E11" s="41">
-        <v>9</v>
-      </c>
-      <c r="F11" s="38">
-        <v>40</v>
-      </c>
-      <c r="G11" s="2">
-        <v>10</v>
-      </c>
-      <c r="H11" s="2">
-        <v>3</v>
-      </c>
-      <c r="I11" s="2">
-        <v>10</v>
-      </c>
-      <c r="J11" s="36"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="42"/>
-      <c r="S11" s="42"/>
-      <c r="T11" s="42"/>
-      <c r="U11" s="42"/>
-      <c r="V11" s="42"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2" t="s">
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="32"/>
+      <c r="T11" s="32"/>
+      <c r="U11" s="32"/>
+      <c r="V11" s="32"/>
+      <c r="W11" s="32"/>
+      <c r="X11" s="32"/>
+      <c r="Y11" s="32"/>
+      <c r="Z11" s="32"/>
+      <c r="AA11" s="32"/>
+      <c r="AB11" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Assets/Data/DataTable/01_Character_Table.xlsx
+++ b/Assets/Data/DataTable/01_Character_Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB88A94-BF85-4295-B528-D7EC1ECB053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FA9F07-F50C-4FCA-9A41-5B147B9423BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9C87D5F5-8BEA-4097-972C-AE5594D6987B}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{9C87D5F5-8BEA-4097-972C-AE5594D6987B}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="3" r:id="rId1"/>
@@ -39,31 +39,371 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={AF605D7A-2772-4B6B-9D24-C9A48EDF7BB3}</author>
-    <author>tc={ADC7BD43-605B-4A15-B63F-C1772D243909}</author>
+    <author>전세혁</author>
   </authors>
   <commentList>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{AF605D7A-2772-4B6B-9D24-C9A48EDF7BB3}">
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{4B15E4F2-86B0-4975-BF2D-5AD5A4F04206}">
       <text>
-        <t>[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    1: 물리
-2: 화염
-3: 방사능
-4: 중력
-5: 공허
-6: 신성</t>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>적</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>몬스터의</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>경우</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> 1.0 </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>고정</t>
+        </r>
       </text>
     </comment>
-    <comment ref="C4" authorId="1" shapeId="0" xr:uid="{ADC7BD43-605B-4A15-B63F-C1772D243909}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{444729E2-B726-435D-AF58-113BDDB72C54}">
       <text>
-        <t>[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    0: None
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>0: None
 1: Player
 2: Enemy</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{AA2DD63D-AE36-438C-886C-4A1EF1CD51BF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">물리
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">화염
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">방사능
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">4: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">중력
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">5: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">공허
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">6: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{A179053C-DBDB-44F0-95AF-12EC888AF579}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">물리
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">화염
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">방사능
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">4: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">중력
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">5: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">공허
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">6: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신성</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -71,7 +411,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="116">
   <si>
     <t>칼럼명</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -493,6 +833,30 @@
   </si>
   <si>
     <t>1.0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 데미지 배율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Critical_Chance</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Critical_Damage_Rate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>카운터 데미지 배율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Counter_Damage_Rate</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -500,7 +864,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="0.0_);[Red]\(0.0\)"/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -559,10 +926,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="12">
@@ -699,7 +1075,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -757,12 +1133,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -798,6 +1168,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3980,9 +4359,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="동우 제" id="{2012398A-2417-46A6-866B-A42EF62887C4}" userId="b4acf424e0b596a4" providerId="Windows Live"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4300,24 +4677,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="K3" dT="2025-10-22T06:27:13.54" personId="{2012398A-2417-46A6-866B-A42EF62887C4}" id="{AF605D7A-2772-4B6B-9D24-C9A48EDF7BB3}">
-    <text>1: 물리
-2: 화염
-3: 방사능
-4: 중력
-5: 공허
-6: 신성</text>
-  </threadedComment>
-  <threadedComment ref="C4" dT="2025-10-21T06:43:27.45" personId="{2012398A-2417-46A6-866B-A42EF62887C4}" id="{ADC7BD43-605B-4A15-B63F-C1772D243909}">
-    <text>0: None
-1: Player
-2: Enemy</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77C094FC-05DB-4CD8-97F7-07905908E4F3}">
   <sheetPr codeName="Sheet1"/>
@@ -4349,12 +4708,12 @@
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="20"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="32"/>
     </row>
     <row r="2" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
@@ -4612,214 +4971,252 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B84F12-225E-4602-82FB-B79E6E932B4F}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="23.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="20.375" customWidth="1"/>
-    <col min="10" max="10" width="28" style="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="32.5" style="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.125" style="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.125" style="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26" style="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="36.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23" style="17" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23" style="17" customWidth="1"/>
-    <col min="20" max="20" width="21.625" style="17" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.375" style="17" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.75" style="17" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="20.375" style="17" customWidth="1"/>
-    <col min="25" max="25" width="21" customWidth="1"/>
-    <col min="26" max="26" width="31" customWidth="1"/>
-    <col min="27" max="27" width="32" customWidth="1"/>
-    <col min="28" max="28" width="27" customWidth="1"/>
-    <col min="29" max="29" width="20.625" customWidth="1"/>
+    <col min="4" max="11" width="20.375" customWidth="1"/>
+    <col min="12" max="12" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.5" style="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="32.5" style="17" customWidth="1"/>
+    <col min="20" max="20" width="28.125" style="17" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.125" style="17" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26" style="17" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="36.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23" style="17" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23" style="17" customWidth="1"/>
+    <col min="26" max="26" width="21.625" style="17" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.375" style="17" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="25.75" style="17" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="20.375" style="17" customWidth="1"/>
+    <col min="31" max="31" width="21" customWidth="1"/>
+    <col min="32" max="32" width="31" customWidth="1"/>
+    <col min="33" max="33" width="32" customWidth="1"/>
+    <col min="34" max="34" width="27" customWidth="1"/>
+    <col min="35" max="35" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="K2" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="M2" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="N2" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="L2" s="24" t="s">
+      <c r="O2" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="M2" s="24" t="s">
+      <c r="P2" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="Q2" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="24"/>
-      <c r="X2" s="24"/>
-      <c r="Y2" s="24"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="22"/>
+      <c r="AH2" s="22"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="N3" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="O3" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="M3" s="25" t="s">
+      <c r="P3" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="Q3" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25"/>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="23"/>
+      <c r="AC3" s="23"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="23"/>
+      <c r="AG3" s="23"/>
+      <c r="AH3" s="23"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="M4" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="N4" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="O4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="M4" s="28" t="s">
+      <c r="P4" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="N4" s="28" t="s">
+      <c r="Q4" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="26"/>
+      <c r="W4" s="26"/>
+      <c r="X4" s="26"/>
+      <c r="Y4" s="26"/>
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="26"/>
+      <c r="AC4" s="26"/>
+      <c r="AD4" s="26"/>
+      <c r="AE4" s="26"/>
+      <c r="AF4" s="26"/>
+      <c r="AG4" s="26"/>
+      <c r="AH4" s="26"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A5" s="30">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A5" s="28">
         <v>10010001</v>
       </c>
       <c r="B5" s="14" t="s">
@@ -4846,38 +5243,50 @@
       <c r="I5" s="14">
         <v>10</v>
       </c>
-      <c r="J5" s="31" t="s">
+      <c r="J5" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="K5" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="L5" s="33">
+        <v>1.3</v>
+      </c>
+      <c r="M5" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="N5" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="L5" s="31" t="s">
+      <c r="O5" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="M5" s="31" t="s">
+      <c r="P5" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="Q5" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="31"/>
-      <c r="T5" s="31"/>
-      <c r="U5" s="31"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="31"/>
-      <c r="X5" s="31"/>
-      <c r="Y5" s="31"/>
-      <c r="Z5" s="31"/>
-      <c r="AA5" s="31"/>
-      <c r="AB5" s="31"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+      <c r="AF5" s="29"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="29"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="30">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A6" s="28">
         <v>10010002</v>
       </c>
       <c r="B6" s="14" t="s">
@@ -4904,30 +5313,42 @@
       <c r="I6" s="14">
         <v>10</v>
       </c>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="14" t="s">
+      <c r="J6" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="K6" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="L6" s="33">
+        <v>1.3</v>
+      </c>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="31"/>
-      <c r="X6" s="31"/>
-      <c r="Y6" s="31"/>
-      <c r="Z6" s="31"/>
-      <c r="AA6" s="31"/>
-      <c r="AB6" s="31"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A7" s="30">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" s="28">
         <v>10010003</v>
       </c>
       <c r="B7" s="14" t="s">
@@ -4954,31 +5375,43 @@
       <c r="I7" s="14">
         <v>10</v>
       </c>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="14" t="s">
+      <c r="J7" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="K7" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="L7" s="33">
+        <v>1.3</v>
+      </c>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="31"/>
-      <c r="Z7" s="31"/>
-      <c r="AA7" s="31"/>
-      <c r="AB7" s="31"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" s="30">
-        <v>3001001</v>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A8" s="28">
+        <v>30010001</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>90</v>
@@ -5004,31 +5437,43 @@
       <c r="I8" s="14">
         <v>10</v>
       </c>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="14" t="s">
+      <c r="J8" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="K8" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="L8" s="33">
+        <v>1</v>
+      </c>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="O8" s="32"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="32"/>
-      <c r="R8" s="32"/>
-      <c r="S8" s="32"/>
-      <c r="T8" s="32"/>
-      <c r="U8" s="32"/>
-      <c r="V8" s="32"/>
-      <c r="W8" s="32"/>
-      <c r="X8" s="32"/>
-      <c r="Y8" s="32"/>
-      <c r="Z8" s="32"/>
-      <c r="AA8" s="32"/>
-      <c r="AB8" s="32"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="30"/>
+      <c r="AH8" s="30"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" s="30">
-        <v>3001002</v>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" s="28">
+        <v>30010002</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>92</v>
@@ -5054,31 +5499,43 @@
       <c r="I9" s="14">
         <v>10</v>
       </c>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="14" t="s">
+      <c r="J9" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="K9" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="L9" s="33">
+        <v>1</v>
+      </c>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="O9" s="32"/>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="32"/>
-      <c r="R9" s="32"/>
-      <c r="S9" s="32"/>
-      <c r="T9" s="32"/>
-      <c r="U9" s="32"/>
-      <c r="V9" s="32"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="32"/>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="32"/>
-      <c r="AA9" s="32"/>
-      <c r="AB9" s="32"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" s="30">
-        <v>3001003</v>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10" s="28">
+        <v>30010003</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>94</v>
@@ -5104,31 +5561,43 @@
       <c r="I10" s="14">
         <v>10</v>
       </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="14" t="s">
+      <c r="J10" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="K10" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="L10" s="33">
+        <v>1</v>
+      </c>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="32"/>
-      <c r="R10" s="32"/>
-      <c r="S10" s="32"/>
-      <c r="T10" s="32"/>
-      <c r="U10" s="32"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="32"/>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="32"/>
-      <c r="AA10" s="32"/>
-      <c r="AB10" s="32"/>
+      <c r="R10" s="30"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
+      <c r="AA10" s="30"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="30"/>
+      <c r="AD10" s="30"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="30"/>
+      <c r="AH10" s="30"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" s="30">
-        <v>3001004</v>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A11" s="28">
+        <v>30010004</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>96</v>
@@ -5154,27 +5623,39 @@
       <c r="I11" s="14">
         <v>10</v>
       </c>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="14" t="s">
+      <c r="J11" s="14">
+        <v>0.3</v>
+      </c>
+      <c r="K11" s="14">
+        <v>1.3</v>
+      </c>
+      <c r="L11" s="33">
+        <v>1</v>
+      </c>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
-      <c r="S11" s="32"/>
-      <c r="T11" s="32"/>
-      <c r="U11" s="32"/>
-      <c r="V11" s="32"/>
-      <c r="W11" s="32"/>
-      <c r="X11" s="32"/>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="32"/>
-      <c r="AA11" s="32"/>
-      <c r="AB11" s="32"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="30"/>
+      <c r="AD11" s="30"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="30"/>
+      <c r="AH11" s="30"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
